--- a/outputs/M7a_human_capital_robustness_from_M2_regression_detail.xlsx
+++ b/outputs/M7a_human_capital_robustness_from_M2_regression_detail.xlsx
@@ -40,22 +40,22 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>inflation_gdp_deflator_pct</t>
+  </si>
+  <si>
+    <t>trade_pct_gdp</t>
+  </si>
+  <si>
+    <t>ln_gdppc</t>
+  </si>
+  <si>
+    <t>xr_dep_pct</t>
+  </si>
+  <si>
     <t>broad_money_pct_gdp</t>
   </si>
   <si>
     <t>deposit_interest_rate_pct</t>
-  </si>
-  <si>
-    <t>inflation_gdp_deflator_pct</t>
-  </si>
-  <si>
-    <t>trade_pct_gdp</t>
-  </si>
-  <si>
-    <t>ln_gdppc</t>
-  </si>
-  <si>
-    <t>xr_dep_pct</t>
   </si>
   <si>
     <t>hc_human_capital_index</t>
@@ -450,19 +450,19 @@
         <v>-33.07313846388985</v>
       </c>
       <c r="C2">
-        <v>17.54373109269799</v>
+        <v>17.54373109267681</v>
       </c>
       <c r="D2">
-        <v>-1.885182706525607</v>
+        <v>-1.885182706527884</v>
       </c>
       <c r="E2">
-        <v>0.06450603440354463</v>
+        <v>0.06450603440323177</v>
       </c>
       <c r="F2">
-        <v>-68.20385400410726</v>
+        <v>-68.20385400406484</v>
       </c>
       <c r="G2">
-        <v>2.057577076327547</v>
+        <v>2.057577076285128</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -470,22 +470,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>1.088606312984268E-05</v>
+        <v>-0.009443020010844306</v>
       </c>
       <c r="C3">
-        <v>0.02805712640429738</v>
+        <v>0.0638159517436284</v>
       </c>
       <c r="D3">
-        <v>0.0003879963675886392</v>
+        <v>-0.1479727208140734</v>
       </c>
       <c r="E3">
-        <v>0.9996917784447774</v>
+        <v>0.8828865130259158</v>
       </c>
       <c r="F3">
-        <v>-0.05617254044843735</v>
+        <v>-0.1372322591292419</v>
       </c>
       <c r="G3">
-        <v>0.05619431257469704</v>
+        <v>0.1183462191075533</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -493,22 +493,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.02448367293269099</v>
+        <v>-0.03283413028254602</v>
       </c>
       <c r="C4">
-        <v>0.1272615178785485</v>
+        <v>0.02224598016256831</v>
       </c>
       <c r="D4">
-        <v>0.1923886603022988</v>
+        <v>-1.475957905320514</v>
       </c>
       <c r="E4">
-        <v>0.8481215794903119</v>
+        <v>0.1454584410213007</v>
       </c>
       <c r="F4">
-        <v>-0.2303531209160473</v>
+        <v>-0.07738093716616201</v>
       </c>
       <c r="G4">
-        <v>0.2793204667814292</v>
+        <v>0.01171267660106996</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -516,22 +516,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-0.009443020010844306</v>
+        <v>4.496914530235127</v>
       </c>
       <c r="C5">
-        <v>0.06381595174362112</v>
+        <v>1.695273828645597</v>
       </c>
       <c r="D5">
-        <v>-0.1479727208140903</v>
+        <v>2.652618387808088</v>
       </c>
       <c r="E5">
-        <v>0.8828865130259025</v>
+        <v>0.01032798595589024</v>
       </c>
       <c r="F5">
-        <v>-0.1372322591292273</v>
+        <v>1.102187244332298</v>
       </c>
       <c r="G5">
-        <v>0.1183462191075387</v>
+        <v>7.891641816137956</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -539,22 +539,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>-0.03283413028254602</v>
+        <v>0.1142320226987247</v>
       </c>
       <c r="C6">
-        <v>0.02224598016256763</v>
+        <v>0.04687305473503152</v>
       </c>
       <c r="D6">
-        <v>-1.475957905320559</v>
+        <v>2.437050952716148</v>
       </c>
       <c r="E6">
-        <v>0.1454584410212885</v>
+        <v>0.01795221530653346</v>
       </c>
       <c r="F6">
-        <v>-0.07738093716616065</v>
+        <v>0.02037034962036732</v>
       </c>
       <c r="G6">
-        <v>0.0117126766010686</v>
+        <v>0.2080936957770821</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -562,22 +562,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>4.496914530235127</v>
+        <v>1.088606312984268E-05</v>
       </c>
       <c r="C7">
-        <v>1.695273828648453</v>
+        <v>0.02805712640429694</v>
       </c>
       <c r="D7">
-        <v>2.652618387803618</v>
+        <v>0.0003879963675886453</v>
       </c>
       <c r="E7">
-        <v>0.01032798595601192</v>
+        <v>0.9996917784447774</v>
       </c>
       <c r="F7">
-        <v>1.102187244326578</v>
+        <v>-0.05617254044843647</v>
       </c>
       <c r="G7">
-        <v>7.891641816143676</v>
+        <v>0.05619431257469615</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -585,22 +585,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.1142320226987247</v>
+        <v>0.02448367293269099</v>
       </c>
       <c r="C8">
-        <v>0.04687305473502685</v>
+        <v>0.1272615178785047</v>
       </c>
       <c r="D8">
-        <v>2.437050952716391</v>
+        <v>0.192388660302365</v>
       </c>
       <c r="E8">
-        <v>0.01795221530652258</v>
+        <v>0.8481215794902603</v>
       </c>
       <c r="F8">
-        <v>0.02037034962037668</v>
+        <v>-0.2303531209159596</v>
       </c>
       <c r="G8">
-        <v>0.2080936957770728</v>
+        <v>0.2793204667813416</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -611,19 +611,19 @@
         <v>0.5273139486915152</v>
       </c>
       <c r="C9">
-        <v>2.043674384557899</v>
+        <v>2.043674384558773</v>
       </c>
       <c r="D9">
-        <v>0.2580224876702104</v>
+        <v>0.2580224876701</v>
       </c>
       <c r="E9">
-        <v>0.7973188945592788</v>
+        <v>0.7973188945593634</v>
       </c>
       <c r="F9">
-        <v>-3.565073416423483</v>
+        <v>-3.565073416425234</v>
       </c>
       <c r="G9">
-        <v>4.619701313806513</v>
+        <v>4.619701313808264</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/M7a_human_capital_robustness_from_M2_regression_detail.xlsx
+++ b/outputs/M7a_human_capital_robustness_from_M2_regression_detail.xlsx
@@ -52,7 +52,7 @@
     <t>xr_dep_pct</t>
   </si>
   <si>
-    <t>broad_money_pct_gdp</t>
+    <t>broad_money_growth_pct</t>
   </si>
   <si>
     <t>deposit_interest_rate_pct</t>
@@ -447,22 +447,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>-33.07313846388985</v>
+        <v>-18.52860684455544</v>
       </c>
       <c r="C2">
-        <v>17.54373109267681</v>
+        <v>13.57529452466943</v>
       </c>
       <c r="D2">
-        <v>-1.885182706527884</v>
+        <v>-1.364876969032584</v>
       </c>
       <c r="E2">
-        <v>0.06450603440323177</v>
+        <v>0.1750032382510114</v>
       </c>
       <c r="F2">
-        <v>-68.20385400406484</v>
+        <v>-45.42371372955579</v>
       </c>
       <c r="G2">
-        <v>2.057577076285128</v>
+        <v>8.366500040444905</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -470,22 +470,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>-0.009443020010844306</v>
+        <v>0.001682231950819937</v>
       </c>
       <c r="C3">
-        <v>0.0638159517436284</v>
+        <v>0.04425387850278762</v>
       </c>
       <c r="D3">
-        <v>-0.1479727208140734</v>
+        <v>0.03801320941200602</v>
       </c>
       <c r="E3">
-        <v>0.8828865130259158</v>
+        <v>0.9697442254180242</v>
       </c>
       <c r="F3">
-        <v>-0.1372322591292419</v>
+        <v>-0.08599268296505183</v>
       </c>
       <c r="G3">
-        <v>0.1183462191075533</v>
+        <v>0.08935714686669172</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -493,22 +493,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.03283413028254602</v>
+        <v>-0.01532096300992632</v>
       </c>
       <c r="C4">
-        <v>0.02224598016256831</v>
+        <v>0.01780474219374928</v>
       </c>
       <c r="D4">
-        <v>-1.475957905320514</v>
+        <v>-0.8604990088149133</v>
       </c>
       <c r="E4">
-        <v>0.1454584410213007</v>
+        <v>0.3913361047235093</v>
       </c>
       <c r="F4">
-        <v>-0.07738093716616201</v>
+        <v>-0.05059536854791026</v>
       </c>
       <c r="G4">
-        <v>0.01171267660106996</v>
+        <v>0.01995344252805763</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -516,22 +516,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>4.496914530235127</v>
+        <v>0.9459017470891425</v>
       </c>
       <c r="C5">
-        <v>1.695273828645597</v>
+        <v>0.6208559339574636</v>
       </c>
       <c r="D5">
-        <v>2.652618387808088</v>
+        <v>1.523544666891995</v>
       </c>
       <c r="E5">
-        <v>0.01032798595589024</v>
+        <v>0.1304162563264659</v>
       </c>
       <c r="F5">
-        <v>1.102187244332298</v>
+        <v>-0.2841258352685457</v>
       </c>
       <c r="G5">
-        <v>7.891641816137956</v>
+        <v>2.175929329446831</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -539,22 +539,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.1142320226987247</v>
+        <v>0.0539767276994177</v>
       </c>
       <c r="C6">
-        <v>0.04687305473503152</v>
+        <v>0.04071236312983065</v>
       </c>
       <c r="D6">
-        <v>2.437050952716148</v>
+        <v>1.325806795525166</v>
       </c>
       <c r="E6">
-        <v>0.01795221530653346</v>
+        <v>0.187577619702866</v>
       </c>
       <c r="F6">
-        <v>0.02037034962036732</v>
+        <v>-0.0266818065171286</v>
       </c>
       <c r="G6">
-        <v>0.2080936957770821</v>
+        <v>0.134635261915964</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -562,22 +562,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>1.088606312984268E-05</v>
+        <v>0.04531302892637981</v>
       </c>
       <c r="C7">
-        <v>0.02805712640429694</v>
+        <v>0.03916200199324453</v>
       </c>
       <c r="D7">
-        <v>0.0003879963675886453</v>
+        <v>1.157066202442774</v>
       </c>
       <c r="E7">
-        <v>0.9996917784447774</v>
+        <v>0.2496853940281734</v>
       </c>
       <c r="F7">
-        <v>-0.05617254044843647</v>
+        <v>-0.0322739602564244</v>
       </c>
       <c r="G7">
-        <v>0.05619431257469615</v>
+        <v>0.122900018109184</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -585,22 +585,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.02448367293269099</v>
+        <v>0.08869483621670479</v>
       </c>
       <c r="C8">
-        <v>0.1272615178785047</v>
+        <v>0.1700270820859828</v>
       </c>
       <c r="D8">
-        <v>0.192388660302365</v>
+        <v>0.5216512283134506</v>
       </c>
       <c r="E8">
-        <v>0.8481215794902603</v>
+        <v>0.6029341479399069</v>
       </c>
       <c r="F8">
-        <v>-0.2303531209159596</v>
+        <v>-0.2481594793738138</v>
       </c>
       <c r="G8">
-        <v>0.2793204667813416</v>
+        <v>0.4255491518072234</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -608,22 +608,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.5273139486915152</v>
+        <v>0.1645792046384227</v>
       </c>
       <c r="C9">
-        <v>2.043674384558773</v>
+        <v>3.259585501898097</v>
       </c>
       <c r="D9">
-        <v>0.2580224876701</v>
+        <v>0.05049083834204877</v>
       </c>
       <c r="E9">
-        <v>0.7973188945593634</v>
+        <v>0.9598203914646151</v>
       </c>
       <c r="F9">
-        <v>-3.565073416425234</v>
+        <v>-6.293247571424221</v>
       </c>
       <c r="G9">
-        <v>4.619701313808264</v>
+        <v>6.622405980701066</v>
       </c>
     </row>
   </sheetData>
